--- a/Samlet_byggaktivitet_42-25.xlsx
+++ b/Samlet_byggaktivitet_42-25.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7767ba86a98102bc/TEP4290/Project/TEP4290-project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilnygaardeik/Documents/Industrial_Ecology/V_2026/MFA2/Project/TEP4290-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{0350814F-C5EF-4187-8ABD-4163286983FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC8D138-497A-1E47-AC2B-FE80905A04D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BYGV05A" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>Det samlede boligbyggeri (historisk oversigt) efter byggefase, anvendelse og tid</t>
   </si>
@@ -306,6 +306,15 @@
   </si>
   <si>
     <t>Tot</t>
+  </si>
+  <si>
+    <t>Ratio parcelhus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio rekkehus </t>
+  </si>
+  <si>
+    <t>Ratio etage</t>
   </si>
 </sst>
 </file>
@@ -676,25 +685,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CG8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:CG10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40.73046875" customWidth="1"/>
+    <col min="1" max="1" width="40.6640625" customWidth="1"/>
     <col min="2" max="2" width="30.6640625" customWidth="1"/>
     <col min="3" max="111" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:85" ht="16.899999999999999" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:85" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:85" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:85" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:85" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:85" x14ac:dyDescent="0.2">
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
@@ -945,7 +954,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:85" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:85" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>85</v>
       </c>
@@ -1202,7 +1211,7 @@
         <v>3931</v>
       </c>
     </row>
-    <row r="5" spans="1:85" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:85" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>87</v>
       </c>
@@ -1456,7 +1465,7 @@
         <v>5999</v>
       </c>
     </row>
-    <row r="6" spans="1:85" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:85" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>88</v>
       </c>
@@ -1710,7 +1719,7 @@
         <v>12582</v>
       </c>
     </row>
-    <row r="7" spans="1:85" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:85" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
         <v>90</v>
       </c>
@@ -2047,9 +2056,1018 @@
         <v>22512</v>
       </c>
     </row>
-    <row r="8" spans="1:85" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:85" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>89</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8">
+        <f>C4/C7</f>
+        <v>0.26478739409296065</v>
+      </c>
+      <c r="D8">
+        <f t="shared" ref="D8:BO8" si="63">D4/D7</f>
+        <v>0.2458458296182216</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="63"/>
+        <v>0.2684179104477612</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="63"/>
+        <v>0.35119119603337767</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="63"/>
+        <v>0.42194941263625779</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="63"/>
+        <v>0.28949736469983289</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="63"/>
+        <v>0.24917931883463273</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="63"/>
+        <v>0.28685618126089307</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="63"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="63"/>
+        <v>0.32508515971463464</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="63"/>
+        <v>0.39555252232269805</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="63"/>
+        <v>0.44168421052631579</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="63"/>
+        <v>0.33868387096774194</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="63"/>
+        <v>0.34175947941434115</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="63"/>
+        <v>0.27578086817434577</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="63"/>
+        <v>0.35815100154083207</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="63"/>
+        <v>0.37755151515151514</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="63"/>
+        <v>0.44369305907767448</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="63"/>
+        <v>0.44184326182498584</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="63"/>
+        <v>0.43662429435893269</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="63"/>
+        <v>0.44651466862793171</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="63"/>
+        <v>0.5585936450807123</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="63"/>
+        <v>0.62068514986020018</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="63"/>
+        <v>0.55953837153645691</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="63"/>
+        <v>0.56479223337397988</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" si="63"/>
+        <v>0.47808178199139378</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="63"/>
+        <v>0.49821704627434815</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="63"/>
+        <v>0.48985725018782872</v>
+      </c>
+      <c r="AE8">
+        <f t="shared" si="63"/>
+        <v>0.52341500155066234</v>
+      </c>
+      <c r="AF8">
+        <f t="shared" si="63"/>
+        <v>0.61279032771237674</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="63"/>
+        <v>0.64909160451329129</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="63"/>
+        <v>0.6042149093921948</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="63"/>
+        <v>0.62116180154984557</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="63"/>
+        <v>0.64380773446062312</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="63"/>
+        <v>0.66226986977997304</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="63"/>
+        <v>0.6678456980470403</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="63"/>
+        <v>0.64953472199225093</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="63"/>
+        <v>0.51924061870454463</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="63"/>
+        <v>0.3392379679144385</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="63"/>
+        <v>0.1879092431856251</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="63"/>
+        <v>0.23590383415710928</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="63"/>
+        <v>0.33382905447714467</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="63"/>
+        <v>0.34968347224119872</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="63"/>
+        <v>0.40436895004265105</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="63"/>
+        <v>0.32218316513588086</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="63"/>
+        <v>0.26112615707991432</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="63"/>
+        <v>0.19642211055276382</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="63"/>
+        <v>0.13438985736925516</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="63"/>
+        <v>0.1203752782783844</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="63"/>
+        <v>0.13386673838499294</v>
+      </c>
+      <c r="BA8">
+        <f t="shared" si="63"/>
+        <v>0.12887398806116607</v>
+      </c>
+      <c r="BB8">
+        <f t="shared" si="63"/>
+        <v>0.19574360699865412</v>
+      </c>
+      <c r="BC8">
+        <f t="shared" si="63"/>
+        <v>0.27819673489682606</v>
+      </c>
+      <c r="BD8">
+        <f t="shared" si="63"/>
+        <v>0.3707557061053311</v>
+      </c>
+      <c r="BE8">
+        <f t="shared" si="63"/>
+        <v>0.42023902312288908</v>
+      </c>
+      <c r="BF8">
+        <f t="shared" si="63"/>
+        <v>0.43015493135155564</v>
+      </c>
+      <c r="BG8">
+        <f t="shared" si="63"/>
+        <v>0.44513893606902644</v>
+      </c>
+      <c r="BH8">
+        <f t="shared" si="63"/>
+        <v>0.3831285478192139</v>
+      </c>
+      <c r="BI8">
+        <f t="shared" si="63"/>
+        <v>0.34385591812321392</v>
+      </c>
+      <c r="BJ8">
+        <f t="shared" si="63"/>
+        <v>0.30116186143726564</v>
+      </c>
+      <c r="BK8">
+        <f t="shared" si="63"/>
+        <v>0.27101565826198021</v>
+      </c>
+      <c r="BL8">
+        <f t="shared" si="63"/>
+        <v>0.27854037002301985</v>
+      </c>
+      <c r="BM8">
+        <f t="shared" si="63"/>
+        <v>0.31944154161267402</v>
+      </c>
+      <c r="BN8">
+        <f t="shared" si="63"/>
+        <v>0.36038233882578785</v>
+      </c>
+      <c r="BO8">
+        <f t="shared" si="63"/>
+        <v>0.34186005932647007</v>
+      </c>
+      <c r="BP8">
+        <f t="shared" ref="BP8:CG8" si="64">BP4/BP7</f>
+        <v>0.40393013100436681</v>
+      </c>
+      <c r="BQ8">
+        <f t="shared" si="64"/>
+        <v>0.42337793486493308</v>
+      </c>
+      <c r="BR8">
+        <f t="shared" si="64"/>
+        <v>0.46641977780002003</v>
+      </c>
+      <c r="BS8">
+        <f t="shared" si="64"/>
+        <v>0.4411660777385159</v>
+      </c>
+      <c r="BT8">
+        <f t="shared" si="64"/>
+        <v>0.30161957512444787</v>
+      </c>
+      <c r="BU8">
+        <f t="shared" si="64"/>
+        <v>0.30283841168144232</v>
+      </c>
+      <c r="BV8">
+        <f t="shared" si="64"/>
+        <v>0.30566932528562191</v>
+      </c>
+      <c r="BW8">
+        <f t="shared" si="64"/>
+        <v>0.32892959015162887</v>
+      </c>
+      <c r="BX8">
+        <f t="shared" si="64"/>
+        <v>0.28298966222566202</v>
+      </c>
+      <c r="BY8">
+        <f t="shared" si="64"/>
+        <v>0.24415872312125914</v>
+      </c>
+      <c r="BZ8">
+        <f t="shared" si="64"/>
+        <v>0.21396024825202295</v>
+      </c>
+      <c r="CA8">
+        <f t="shared" si="64"/>
+        <v>0.19222218535355212</v>
+      </c>
+      <c r="CB8">
+        <f t="shared" si="64"/>
+        <v>0.18169406843664673</v>
+      </c>
+      <c r="CC8">
+        <f t="shared" si="64"/>
+        <v>0.2078717663862879</v>
+      </c>
+      <c r="CD8">
+        <f t="shared" si="64"/>
+        <v>0.21269718484957317</v>
+      </c>
+      <c r="CE8">
+        <f t="shared" si="64"/>
+        <v>0.16533482735234276</v>
+      </c>
+      <c r="CF8">
+        <f t="shared" si="64"/>
+        <v>0.14234918098282062</v>
+      </c>
+      <c r="CG8">
+        <f t="shared" si="64"/>
+        <v>0.17461798152096661</v>
+      </c>
+    </row>
+    <row r="9" spans="1:85" x14ac:dyDescent="0.2">
+      <c r="B9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9">
+        <f>C5/C7</f>
+        <v>8.7972127642727063E-2</v>
+      </c>
+      <c r="D9">
+        <f t="shared" ref="D9:BO9" si="65">D5/D7</f>
+        <v>0.11258814946907676</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="65"/>
+        <v>8.6328358208955222E-2</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="65"/>
+        <v>7.1471762002660533E-2</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="65"/>
+        <v>7.1965287331992797E-2</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="65"/>
+        <v>0.12739426661524617</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="65"/>
+        <v>8.3709478867459997E-2</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="65"/>
+        <v>6.9535428811827629E-2</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="65"/>
+        <v>9.6126172796868706E-2</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="65"/>
+        <v>0.10861880583585064</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="65"/>
+        <v>9.1508843769550138E-2</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="65"/>
+        <v>0.1118421052631579</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="65"/>
+        <v>0.11179354838709678</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="65"/>
+        <v>9.6984107120510574E-2</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="65"/>
+        <v>0.11214288887901541</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="65"/>
+        <v>7.7041602465331274E-2</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="65"/>
+        <v>0.10555151515151515</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="65"/>
+        <v>7.4668920822766979E-2</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="65"/>
+        <v>6.440102693529437E-2</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="65"/>
+        <v>7.3346058563132033E-2</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="65"/>
+        <v>7.2321647462613381E-2</v>
+      </c>
+      <c r="X9">
+        <f t="shared" si="65"/>
+        <v>6.5885955252343475E-2</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="65"/>
+        <v>6.932504115602707E-2</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="65"/>
+        <v>7.2515024198266234E-2</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" si="65"/>
+        <v>7.3515617671888189E-2</v>
+      </c>
+      <c r="AB9">
+        <f t="shared" si="65"/>
+        <v>6.4224405734404119E-2</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="65"/>
+        <v>9.1868494280119548E-2</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="65"/>
+        <v>0.10398602960586431</v>
+      </c>
+      <c r="AE9">
+        <f t="shared" si="65"/>
+        <v>0.11550219307961544</v>
+      </c>
+      <c r="AF9">
+        <f t="shared" si="65"/>
+        <v>8.8556580761480541E-2</v>
+      </c>
+      <c r="AG9">
+        <f t="shared" si="65"/>
+        <v>7.6381717345572767E-2</v>
+      </c>
+      <c r="AH9">
+        <f t="shared" si="65"/>
+        <v>0.12343056234199401</v>
+      </c>
+      <c r="AI9">
+        <f t="shared" si="65"/>
+        <v>0.11900600128182719</v>
+      </c>
+      <c r="AJ9">
+        <f t="shared" si="65"/>
+        <v>0.13300454047283544</v>
+      </c>
+      <c r="AK9">
+        <f t="shared" si="65"/>
+        <v>0.19092388863942525</v>
+      </c>
+      <c r="AL9">
+        <f t="shared" si="65"/>
+        <v>0.18362657959973397</v>
+      </c>
+      <c r="AM9">
+        <f t="shared" si="65"/>
+        <v>0.22028678345531014</v>
+      </c>
+      <c r="AN9">
+        <f t="shared" si="65"/>
+        <v>0.24915491515006657</v>
+      </c>
+      <c r="AO9">
+        <f t="shared" si="65"/>
+        <v>0.36440030557677616</v>
+      </c>
+      <c r="AP9">
+        <f t="shared" si="65"/>
+        <v>0.47967108268615805</v>
+      </c>
+      <c r="AQ9">
+        <f t="shared" si="65"/>
+        <v>0.47895772349920823</v>
+      </c>
+      <c r="AR9">
+        <f t="shared" si="65"/>
+        <v>0.43010331872260488</v>
+      </c>
+      <c r="AS9">
+        <f t="shared" si="65"/>
+        <v>0.40365259370587969</v>
+      </c>
+      <c r="AT9">
+        <f t="shared" si="65"/>
+        <v>0.37840744724251751</v>
+      </c>
+      <c r="AU9">
+        <f t="shared" si="65"/>
+        <v>0.43028310088067429</v>
+      </c>
+      <c r="AV9">
+        <f t="shared" si="65"/>
+        <v>0.46097255345810262</v>
+      </c>
+      <c r="AW9">
+        <f t="shared" si="65"/>
+        <v>0.47328643216080402</v>
+      </c>
+      <c r="AX9">
+        <f t="shared" si="65"/>
+        <v>0.49251188589540412</v>
+      </c>
+      <c r="AY9">
+        <f t="shared" si="65"/>
+        <v>0.3849782677833139</v>
+      </c>
+      <c r="AZ9">
+        <f t="shared" si="65"/>
+        <v>0.40294493377260809</v>
+      </c>
+      <c r="BA9">
+        <f t="shared" si="65"/>
+        <v>0.33592280644369943</v>
+      </c>
+      <c r="BB9">
+        <f t="shared" si="65"/>
+        <v>0.27582436069986543</v>
+      </c>
+      <c r="BC9">
+        <f t="shared" si="65"/>
+        <v>0.20253584155133836</v>
+      </c>
+      <c r="BD9">
+        <f t="shared" si="65"/>
+        <v>0.18146624727800628</v>
+      </c>
+      <c r="BE9">
+        <f t="shared" si="65"/>
+        <v>0.22265523512600677</v>
+      </c>
+      <c r="BF9">
+        <f t="shared" si="65"/>
+        <v>0.20348910442121174</v>
+      </c>
+      <c r="BG9">
+        <f t="shared" si="65"/>
+        <v>0.25633534886880904</v>
+      </c>
+      <c r="BH9">
+        <f t="shared" si="65"/>
+        <v>0.26693971401882588</v>
+      </c>
+      <c r="BI9">
+        <f t="shared" si="65"/>
+        <v>0.28630291752508807</v>
+      </c>
+      <c r="BJ9">
+        <f t="shared" si="65"/>
+        <v>0.3101370873547673</v>
+      </c>
+      <c r="BK9">
+        <f t="shared" si="65"/>
+        <v>0.35522020909219926</v>
+      </c>
+      <c r="BL9">
+        <f t="shared" si="65"/>
+        <v>0.31648051837326285</v>
+      </c>
+      <c r="BM9">
+        <f t="shared" si="65"/>
+        <v>0.28725494294193871</v>
+      </c>
+      <c r="BN9">
+        <f t="shared" si="65"/>
+        <v>0.26319788833786595</v>
+      </c>
+      <c r="BO9">
+        <f t="shared" si="65"/>
+        <v>0.24592566742278835</v>
+      </c>
+      <c r="BP9">
+        <f t="shared" ref="BP9:CG9" si="66">BP5/BP7</f>
+        <v>0.28298655706824216</v>
+      </c>
+      <c r="BQ9">
+        <f t="shared" si="66"/>
+        <v>0.23081292602878062</v>
+      </c>
+      <c r="BR9">
+        <f t="shared" si="66"/>
+        <v>0.14963467120408366</v>
+      </c>
+      <c r="BS9">
+        <f t="shared" si="66"/>
+        <v>0.1993816254416961</v>
+      </c>
+      <c r="BT9">
+        <f t="shared" si="66"/>
+        <v>0.19252611652527518</v>
+      </c>
+      <c r="BU9">
+        <f t="shared" si="66"/>
+        <v>0.19213290620576623</v>
+      </c>
+      <c r="BV9">
+        <f t="shared" si="66"/>
+        <v>0.20054609470431847</v>
+      </c>
+      <c r="BW9">
+        <f t="shared" si="66"/>
+        <v>0.22954511334634439</v>
+      </c>
+      <c r="BX9">
+        <f t="shared" si="66"/>
+        <v>0.18652219580960805</v>
+      </c>
+      <c r="BY9">
+        <f t="shared" si="66"/>
+        <v>0.1887386388827311</v>
+      </c>
+      <c r="BZ9">
+        <f t="shared" si="66"/>
+        <v>0.20017283368685679</v>
+      </c>
+      <c r="CA9">
+        <f t="shared" si="66"/>
+        <v>0.19899127318578491</v>
+      </c>
+      <c r="CB9">
+        <f t="shared" si="66"/>
+        <v>0.19613083134839945</v>
+      </c>
+      <c r="CC9">
+        <f t="shared" si="66"/>
+        <v>0.23783526424377083</v>
+      </c>
+      <c r="CD9">
+        <f t="shared" si="66"/>
+        <v>0.21888554300080118</v>
+      </c>
+      <c r="CE9">
+        <f t="shared" si="66"/>
+        <v>0.24217851561348155</v>
+      </c>
+      <c r="CF9">
+        <f t="shared" si="66"/>
+        <v>0.2675189772273272</v>
+      </c>
+      <c r="CG9">
+        <f t="shared" si="66"/>
+        <v>0.26648009950248758</v>
+      </c>
+    </row>
+    <row r="10" spans="1:85" x14ac:dyDescent="0.2">
+      <c r="B10" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10">
+        <f>C6/C7</f>
+        <v>0.6472404782643123</v>
+      </c>
+      <c r="D10">
+        <f t="shared" ref="D10:BO10" si="67">D6/D7</f>
+        <v>0.64156602091270165</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="67"/>
+        <v>0.64525373134328357</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="67"/>
+        <v>0.57733704196396174</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="67"/>
+        <v>0.50608530003174934</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="67"/>
+        <v>0.58310836868492089</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="67"/>
+        <v>0.66711120229790721</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="67"/>
+        <v>0.64360838992727931</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="67"/>
+        <v>0.57054049386979799</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="67"/>
+        <v>0.56629603444951471</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="67"/>
+        <v>0.51293863390775185</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="67"/>
+        <v>0.4464736842105263</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="67"/>
+        <v>0.54952258064516124</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="67"/>
+        <v>0.56125641346514832</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="67"/>
+        <v>0.61207624294663887</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="67"/>
+        <v>0.56480739599383667</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="67"/>
+        <v>0.51689696969696974</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="67"/>
+        <v>0.48163802009955858</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="67"/>
+        <v>0.49375571123971979</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="67"/>
+        <v>0.49002964707793528</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="67"/>
+        <v>0.48116368390945491</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="67"/>
+        <v>0.37552039966694423</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="67"/>
+        <v>0.30998980898377276</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="67"/>
+        <v>0.36794660426527681</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="67"/>
+        <v>0.36169214895413188</v>
+      </c>
+      <c r="AB10">
+        <f t="shared" si="67"/>
+        <v>0.45769381227420208</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="67"/>
+        <v>0.40991445944553229</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="67"/>
+        <v>0.406156720206307</v>
+      </c>
+      <c r="AE10">
+        <f t="shared" si="67"/>
+        <v>0.3610828053697222</v>
+      </c>
+      <c r="AF10">
+        <f t="shared" si="67"/>
+        <v>0.29865309152614278</v>
+      </c>
+      <c r="AG10">
+        <f t="shared" si="67"/>
+        <v>0.27452667814113596</v>
+      </c>
+      <c r="AH10">
+        <f t="shared" si="67"/>
+        <v>0.27235452826581125</v>
+      </c>
+      <c r="AI10">
+        <f t="shared" si="67"/>
+        <v>0.25983219716832723</v>
+      </c>
+      <c r="AJ10">
+        <f t="shared" si="67"/>
+        <v>0.22318772506654141</v>
+      </c>
+      <c r="AK10">
+        <f t="shared" si="67"/>
+        <v>0.14680624158060171</v>
+      </c>
+      <c r="AL10">
+        <f t="shared" si="67"/>
+        <v>0.1485277223532257</v>
+      </c>
+      <c r="AM10">
+        <f t="shared" si="67"/>
+        <v>0.13017849455243899</v>
+      </c>
+      <c r="AN10">
+        <f t="shared" si="67"/>
+        <v>0.23160446614538874</v>
+      </c>
+      <c r="AO10">
+        <f t="shared" si="67"/>
+        <v>0.29636172650878534</v>
+      </c>
+      <c r="AP10">
+        <f t="shared" si="67"/>
+        <v>0.33241967412821682</v>
+      </c>
+      <c r="AQ10">
+        <f t="shared" si="67"/>
+        <v>0.28513844234368252</v>
+      </c>
+      <c r="AR10">
+        <f t="shared" si="67"/>
+        <v>0.23606762680025048</v>
+      </c>
+      <c r="AS10">
+        <f t="shared" si="67"/>
+        <v>0.24666393405292161</v>
+      </c>
+      <c r="AT10">
+        <f t="shared" si="67"/>
+        <v>0.21722360271483143</v>
+      </c>
+      <c r="AU10">
+        <f t="shared" si="67"/>
+        <v>0.24753373398344483</v>
+      </c>
+      <c r="AV10">
+        <f t="shared" si="67"/>
+        <v>0.27790128946198311</v>
+      </c>
+      <c r="AW10">
+        <f t="shared" si="67"/>
+        <v>0.33029145728643217</v>
+      </c>
+      <c r="AX10">
+        <f t="shared" si="67"/>
+        <v>0.37309825673534075</v>
+      </c>
+      <c r="AY10">
+        <f t="shared" si="67"/>
+        <v>0.4946464539383017</v>
+      </c>
+      <c r="AZ10">
+        <f t="shared" si="67"/>
+        <v>0.46318832784239899</v>
+      </c>
+      <c r="BA10">
+        <f t="shared" si="67"/>
+        <v>0.53520320549513456</v>
+      </c>
+      <c r="BB10">
+        <f t="shared" si="67"/>
+        <v>0.5284320323014805</v>
+      </c>
+      <c r="BC10">
+        <f t="shared" si="67"/>
+        <v>0.51926742355183564</v>
+      </c>
+      <c r="BD10">
+        <f t="shared" si="67"/>
+        <v>0.44777804661666265</v>
+      </c>
+      <c r="BE10">
+        <f t="shared" si="67"/>
+        <v>0.35710574175110416</v>
+      </c>
+      <c r="BF10">
+        <f t="shared" si="67"/>
+        <v>0.36635596422723266</v>
+      </c>
+      <c r="BG10">
+        <f t="shared" si="67"/>
+        <v>0.29852571506216458</v>
+      </c>
+      <c r="BH10">
+        <f t="shared" si="67"/>
+        <v>0.34993173816196022</v>
+      </c>
+      <c r="BI10">
+        <f t="shared" si="67"/>
+        <v>0.369841164351698</v>
+      </c>
+      <c r="BJ10">
+        <f t="shared" si="67"/>
+        <v>0.38870105120796705</v>
+      </c>
+      <c r="BK10">
+        <f t="shared" si="67"/>
+        <v>0.37376413264582053</v>
+      </c>
+      <c r="BL10">
+        <f t="shared" si="67"/>
+        <v>0.4049791116037173</v>
+      </c>
+      <c r="BM10">
+        <f t="shared" si="67"/>
+        <v>0.39330351544538728</v>
+      </c>
+      <c r="BN10">
+        <f t="shared" si="67"/>
+        <v>0.3764197728363462</v>
+      </c>
+      <c r="BO10">
+        <f t="shared" si="67"/>
+        <v>0.41221427325074156</v>
+      </c>
+      <c r="BP10">
+        <f t="shared" ref="BP10:CG10" si="68">BP6/BP7</f>
+        <v>0.31308331192739103</v>
+      </c>
+      <c r="BQ10">
+        <f t="shared" si="68"/>
+        <v>0.3458091391062863</v>
+      </c>
+      <c r="BR10">
+        <f t="shared" si="68"/>
+        <v>0.38394555099589633</v>
+      </c>
+      <c r="BS10">
+        <f t="shared" si="68"/>
+        <v>0.35945229681978796</v>
+      </c>
+      <c r="BT10">
+        <f t="shared" si="68"/>
+        <v>0.50585430835027689</v>
+      </c>
+      <c r="BU10">
+        <f t="shared" si="68"/>
+        <v>0.5050286821127915</v>
+      </c>
+      <c r="BV10">
+        <f t="shared" si="68"/>
+        <v>0.49378458001005965</v>
+      </c>
+      <c r="BW10">
+        <f t="shared" si="68"/>
+        <v>0.44152529650202671</v>
+      </c>
+      <c r="BX10">
+        <f t="shared" si="68"/>
+        <v>0.53048814196472993</v>
+      </c>
+      <c r="BY10">
+        <f t="shared" si="68"/>
+        <v>0.5671026379960098</v>
+      </c>
+      <c r="BZ10">
+        <f t="shared" si="68"/>
+        <v>0.58586691806112023</v>
+      </c>
+      <c r="CA10">
+        <f t="shared" si="68"/>
+        <v>0.60878654146066302</v>
+      </c>
+      <c r="CB10">
+        <f t="shared" si="68"/>
+        <v>0.62217510021495381</v>
+      </c>
+      <c r="CC10">
+        <f t="shared" si="68"/>
+        <v>0.55429296936994132</v>
+      </c>
+      <c r="CD10">
+        <f t="shared" si="68"/>
+        <v>0.56841727214962567</v>
+      </c>
+      <c r="CE10">
+        <f t="shared" si="68"/>
+        <v>0.59248665703417569</v>
+      </c>
+      <c r="CF10">
+        <f t="shared" si="68"/>
+        <v>0.59013184178985223</v>
+      </c>
+      <c r="CG10">
+        <f t="shared" si="68"/>
+        <v>0.55890191897654584</v>
       </c>
     </row>
   </sheetData>

--- a/Samlet_byggaktivitet_42-25.xlsx
+++ b/Samlet_byggaktivitet_42-25.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilnygaardeik/Documents/Industrial_Ecology/V_2026/MFA2/Project/TEP4290-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC8D138-497A-1E47-AC2B-FE80905A04D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44295A62-B860-864C-9213-0450911BA7CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BYGV05A" sheetId="2" r:id="rId1"/>
@@ -308,13 +308,13 @@
     <t>Tot</t>
   </si>
   <si>
-    <t>Ratio parcelhus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ratio rekkehus </t>
-  </si>
-  <si>
-    <t>Ratio etage</t>
+    <t>Ratio_parcelhus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio_rekkehus </t>
+  </si>
+  <si>
+    <t>Ratio_etage</t>
   </si>
 </sst>
 </file>
